--- a/9992.HK.xlsx
+++ b/9992.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F72AD97-6A50-4274-AA3F-811FFFE4BAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689299B8-9A74-49F1-8AE3-F72C75FBD650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{F40E76A4-D28F-40CA-8C98-C80E8AA59D98}"/>
+    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{F40E76A4-D28F-40CA-8C98-C80E8AA59D98}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>266.8</v>
+        <v>154.19999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -632,7 +632,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>354602.81280000001</v>
+        <v>204946.60319999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -673,7 +673,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>340837.1018</v>
+        <v>191180.89219999997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">

--- a/9992.HK.xlsx
+++ b/9992.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689299B8-9A74-49F1-8AE3-F72C75FBD650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A77797-80A8-4C05-B43E-0D52BEB41F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{F40E76A4-D28F-40CA-8C98-C80E8AA59D98}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F40E76A4-D28F-40CA-8C98-C80E8AA59D98}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>154.19999999999999</v>
+        <v>160.9</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -632,7 +632,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>204946.60319999998</v>
+        <v>213851.54640000002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -673,7 +673,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>191180.89219999997</v>
+        <v>200085.83540000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
